--- a/src/test/resources/testdata/LoginData.xlsx
+++ b/src/test/resources/testdata/LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\seleniumjava\org.magnitia.selenium\org.myproject\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91C6A846-6C5E-42BA-B7DA-161933630590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D05B969-9D74-428E-8F86-9B2CFA2ADA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B1E5400C-B87E-425E-8A56-839923AF2FB6}"/>
   </bookViews>
